--- a/data/trans_orig/P13A_1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) en 2023</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23191</t>
+          <t>22944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>496827</t>
+          <t>496697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502222</t>
+          <t>502223</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424798</t>
+          <t>425764</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>438972</t>
+          <t>439191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>925947</t>
+          <t>926194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>940180</t>
+          <t>940264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>445218</t>
+          <t>444310</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363318</t>
+          <t>363878</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374317</t>
+          <t>374765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>812987</t>
+          <t>812586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>824590</t>
+          <t>824224</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17051</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34580</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>650376</t>
+          <t>650145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665931</t>
+          <t>665392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145841</t>
+          <t>144079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159166</t>
+          <t>158937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>799192</t>
+          <t>800339</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>826107</t>
+          <t>827205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53623</t>
+          <t>52900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>33934</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66153</t>
+          <t>65314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1010829</t>
+          <t>1010195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1025083</t>
+          <t>1025271</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>937407</t>
+          <t>937408</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>921818</t>
+          <t>922542</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>957327</t>
+          <t>958370</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1941608</t>
+          <t>1942447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1973053</t>
+          <t>1973827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975441</t>
+          <t>975442</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>975441</t>
+          <t>975442</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>975441</t>
+          <t>975442</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34815</t>
+          <t>35149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70354</t>
+          <t>70596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45964</t>
+          <t>44490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81394</t>
+          <t>83683</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>452178</t>
+          <t>451792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467334</t>
+          <t>466999</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>766506</t>
+          <t>766264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>802045</t>
+          <t>801711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1228065</t>
+          <t>1225776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1263495</t>
+          <t>1264969</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24524</t>
+          <t>23973</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28187</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231863</t>
+          <t>232164</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>239678</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>733464</t>
+          <t>734015</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>746541</t>
+          <t>746636</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>970308</t>
+          <t>971531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>985261</t>
+          <t>985807</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24882</t>
+          <t>26034</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51906</t>
+          <t>52623</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>114517</t>
+          <t>113275</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171269</t>
+          <t>169131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>148670</t>
+          <t>149751</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>210216</t>
+          <t>211009</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3313722</t>
+          <t>3313005</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3340746</t>
+          <t>3339594</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3393896</t>
+          <t>3396034</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3450648</t>
+          <t>3451890</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6720577</t>
+          <t>6719784</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6782123</t>
+          <t>6781042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13A_1_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20988</t>
+          <t>22678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22944</t>
+          <t>26655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>500669</t>
+          <t>545184</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>496697</t>
+          <t>540720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502223</t>
+          <t>547111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>433864</t>
+          <t>471085</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425764</t>
+          <t>462697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>439191</t>
+          <t>476948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>934532</t>
+          <t>1016269</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>926194</t>
+          <t>1006413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>940264</t>
+          <t>1022186</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>502386</t>
+          <t>547693</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>502386</t>
+          <t>547693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>502386</t>
+          <t>547693</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446752</t>
+          <t>485375</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446752</t>
+          <t>485375</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446752</t>
+          <t>485375</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>949138</t>
+          <t>1033068</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>949138</t>
+          <t>1033068</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>949138</t>
+          <t>1033068</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17901</t>
+          <t>18987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19582</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>449415</t>
+          <t>480124</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>444310</t>
+          <t>476000</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>450389</t>
+          <t>481151</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>369981</t>
+          <t>410025</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363878</t>
+          <t>403295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374765</t>
+          <t>414825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>819396</t>
+          <t>890150</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>812586</t>
+          <t>883545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>824224</t>
+          <t>895581</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>450389</t>
+          <t>481151</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>450389</t>
+          <t>481151</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>450389</t>
+          <t>481151</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381779</t>
+          <t>422282</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381779</t>
+          <t>422282</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381779</t>
+          <t>422282</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>832168</t>
+          <t>903433</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>832168</t>
+          <t>903433</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>832168</t>
+          <t>903433</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>24170</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20496</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33433</t>
+          <t>34053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>659238</t>
+          <t>462575</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>650145</t>
+          <t>454260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665392</t>
+          <t>466795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>154039</t>
+          <t>173546</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144079</t>
+          <t>162759</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158937</t>
+          <t>179144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>813276</t>
+          <t>636121</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>800339</t>
+          <t>623622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827205</t>
+          <t>643455</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667427</t>
+          <t>470747</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833772</t>
+          <t>657675</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833772</t>
+          <t>657675</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833772</t>
+          <t>657675</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>22108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38034</t>
+          <t>43468</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>32476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52900</t>
+          <t>56110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>50772</t>
+          <t>56745</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65314</t>
+          <t>72337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1019582</t>
+          <t>1114584</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1010195</t>
+          <t>1105753</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1025271</t>
+          <t>1120691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>937408</t>
+          <t>814892</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>922542</t>
+          <t>802250</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>958370</t>
+          <t>825884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1956989</t>
+          <t>1929475</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1942447</t>
+          <t>1913883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1973827</t>
+          <t>1942467</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1032320</t>
+          <t>1127861</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1032320</t>
+          <t>1127861</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1032320</t>
+          <t>1127861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975442</t>
+          <t>858360</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>975442</t>
+          <t>858360</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>975442</t>
+          <t>858360</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2007761</t>
+          <t>1986220</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2007761</t>
+          <t>1986220</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2007761</t>
+          <t>1986220</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20807</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>51506</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35149</t>
+          <t>40475</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70596</t>
+          <t>66445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>60702</t>
+          <t>63375</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44490</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83683</t>
+          <t>80035</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>461769</t>
+          <t>553573</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>451792</t>
+          <t>544759</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466999</t>
+          <t>559889</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>786988</t>
+          <t>774042</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>766264</t>
+          <t>759103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>801711</t>
+          <t>785073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1248757</t>
+          <t>1327615</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1225776</t>
+          <t>1310955</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1264969</t>
+          <t>1340990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472599</t>
+          <t>565442</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472599</t>
+          <t>565442</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472599</t>
+          <t>565442</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>836860</t>
+          <t>825548</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>836860</t>
+          <t>825548</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>836860</t>
+          <t>825548</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1309459</t>
+          <t>1390990</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1309459</t>
+          <t>1390990</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1309459</t>
+          <t>1390990</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,22 +2440,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>815</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23973</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,17 +2510,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>14376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26964</t>
+          <t>29911</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>237563</t>
+          <t>234173</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232164</t>
+          <t>228207</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239678</t>
+          <t>236413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>741354</t>
+          <t>822822</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>734015</t>
+          <t>815250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>746636</t>
+          <t>829243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,17 +2623,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>978917</t>
+          <t>1056996</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>971531</t>
+          <t>1048178</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>985807</t>
+          <t>1063713</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>757988</t>
+          <t>840861</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>757988</t>
+          <t>840861</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>757988</t>
+          <t>840861</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>998495</t>
+          <t>1078089</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>998495</t>
+          <t>1078089</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>998495</t>
+          <t>1078089</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26034</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52623</t>
+          <t>54418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>141533</t>
+          <t>152942</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113275</t>
+          <t>132213</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169131</t>
+          <t>173161</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>178926</t>
+          <t>192850</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>149751</t>
+          <t>168372</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>211009</t>
+          <t>219773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3328235</t>
+          <t>3390213</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3313005</t>
+          <t>3375703</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3339594</t>
+          <t>3401058</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3423632</t>
+          <t>3466413</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3396034</t>
+          <t>3446194</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3451890</t>
+          <t>3487142</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6751867</t>
+          <t>6856626</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6719784</t>
+          <t>6829703</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6781042</t>
+          <t>6881104</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3365628</t>
+          <t>3430121</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3365628</t>
+          <t>3430121</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3365628</t>
+          <t>3430121</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3565165</t>
+          <t>3619355</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3565165</t>
+          <t>3619355</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3565165</t>
+          <t>3619355</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6930793</t>
+          <t>7049476</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6930793</t>
+          <t>7049476</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6930793</t>
+          <t>7049476</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
